--- a/data/conf_snap_output/conf_snap_mu.xlsx
+++ b/data/conf_snap_output/conf_snap_mu.xlsx
@@ -426,16 +426,16 @@
         <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I2">
-        <v>0.98</v>
+        <v>0.949</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.9</v>
+        <v>0.893</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -490,16 +490,16 @@
         <v>0.05</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.002518891687657431</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.9974811083123426</v>
       </c>
       <c r="I4">
-        <v>0.24</v>
+        <v>0.206</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -528,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -554,16 +554,16 @@
         <v>0.05</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>0.05</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -618,16 +618,16 @@
         <v>0.05</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -650,16 +650,16 @@
         <v>0.05</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -682,16 +682,16 @@
         <v>0.05</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
